--- a/4. Supervised Learning (modeling and evaluation)/biases_layer3.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer3.xlsx
@@ -435,17 +435,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.1021038377070604</v>
+        <v>-0.1474673524020174</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.03268697751397927</v>
+        <v>-0.04965983848697263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.1662614063956482</v>
+        <v>0.2325542095161121</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/biases_layer3.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer3.xlsx
@@ -435,17 +435,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.1474673524020174</v>
+        <v>0.08802472557736425</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.04965983848697263</v>
+        <v>0.05923490348359487</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.2325542095161121</v>
+        <v>0.2141580795225266</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/biases_layer3.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer3.xlsx
@@ -435,17 +435,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.08802472557736425</v>
+        <v>-0.1475607053433714</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.05923490348359487</v>
+        <v>0.1402580875077184</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.2141580795225266</v>
+        <v>-0.005954741185111224</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/biases_layer3.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer3.xlsx
@@ -435,17 +435,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.1475607053433714</v>
+        <v>-0.003066693085126095</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1402580875077184</v>
+        <v>-0.02167816910447615</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.005954741185111224</v>
+        <v>-0.2094958479619278</v>
       </c>
     </row>
   </sheetData>
